--- a/public/test-data/02_팀원_테스트.xlsx
+++ b/public/test-data/02_팀원_테스트.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="팀원양식" sheetId="1" r:id="Ra5dc4ae59d534146"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="팀원양식" sheetId="1" r:id="Ra0b368fe125a4313"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,10 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="0"/>
-  </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -24,22 +21,16 @@
     <x:font>
       <x:b/>
       <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF111827"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FF111827"/>
-      <x:name val="Arial"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -48,7 +39,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF111827"/>
+        <x:fgColor rgb="FFF3F4F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -72,7 +68,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -86,25 +82,20 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -308,15 +299,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.78000020980835" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34.439998626708984" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
+    <x:row r="1" ht="21" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>이름</x:v>
       </x:c>
@@ -336,7 +327,7 @@
         <x:v>코멘트</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="25" customHeight="1">
+    <x:row r="2" ht="21" customHeight="1">
       <x:c r="A2" s="12" t="str">
         <x:v>김민준</x:v>
       </x:c>
@@ -346,17 +337,17 @@
       <x:c r="C2" s="13" t="str">
         <x:v>과장</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="n">
+      <x:c r="D2" s="13" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E2" s="13" t="str">
-        <x:v>서비스 기획·PM</x:v>
-      </x:c>
-      <x:c r="F2" s="13" t="str">
-        <x:v>평가 운영 총괄</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="E2" s="12" t="str">
+        <x:v>UX 기획</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>평가 총괄 및 핵심 과제 리드</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
       <x:c r="A3" s="12" t="str">
         <x:v>이서연</x:v>
       </x:c>
@@ -366,17 +357,17 @@
       <x:c r="C3" s="13" t="str">
         <x:v>대리</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="n">
+      <x:c r="D3" s="13" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="str">
+      <x:c r="E3" s="12" t="str">
         <x:v>UX 디자인</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="str">
-        <x:v>사용자 리서치 및 UI 설계</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="25" customHeight="1">
+      <x:c r="F3" s="12" t="str">
+        <x:v>서비스 경험 개선 담당</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
       <x:c r="A4" s="12" t="str">
         <x:v>박지훈</x:v>
       </x:c>
@@ -384,47 +375,67 @@
         <x:v>팀원</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
-        <x:v>대리</x:v>
-      </x:c>
-      <x:c r="D4" s="14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E4" s="13" t="str">
-        <x:v>프론트엔드 개발</x:v>
-      </x:c>
-      <x:c r="F4" s="13" t="str">
-        <x:v>웹 접근성 및 성능 개선</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="25" customHeight="1">
+        <x:v>과장</x:v>
+      </x:c>
+      <x:c r="D4" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="str">
+        <x:v>UI 디자인</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
+        <x:v>디자인 시스템 운영 담당</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
       <x:c r="A5" s="12" t="str">
         <x:v>최유진</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
+        <x:v>PM</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>차장</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>프로젝트 관리</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
+        <x:v>프로젝트 일정 및 협업 관리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" s="12" t="str">
+        <x:v>정하늘</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="str">
         <x:v>팀원</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="str">
-        <x:v>사원</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E5" s="13" t="str">
-        <x:v>콘텐츠·데이터 분석</x:v>
-      </x:c>
-      <x:c r="F5" s="13" t="str">
-        <x:v>콘텐츠 운영 및 지표 분석</x:v>
+      <x:c r="C6" s="13" t="str">
+        <x:v>대리</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>UX 리서치</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>사용자 조사 및 데이터 분석</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
-    <x:dataValidation type="list" sqref="B2:B5">
+    <x:dataValidation type="list" sqref="B2:B6">
       <x:formula1>"팀장,PM,PL,팀원"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C2:C5">
+    <x:dataValidation type="list" sqref="C2:C6">
       <x:formula1>"사원,대리,과장,차장"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="D2:D5">
+    <x:dataValidation type="whole" operator="between" sqref="D2:D6">
       <x:formula1>0</x:formula1>
       <x:formula2>50</x:formula2>
     </x:dataValidation>

--- a/public/test-data/02_팀원_테스트.xlsx
+++ b/public/test-data/02_팀원_테스트.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="팀원양식" sheetId="1" r:id="Ra0b368fe125a4313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="팀원양식" sheetId="1" r:id="R2e2d327e2e714de5"/>
   </x:sheets>
 </x:workbook>
 </file>
